--- a/results_table.xlsx
+++ b/results_table.xlsx
@@ -3901,7 +3901,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>314.64,577.64,513.64</t>
+          <t>314.64,513.64,577.64</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3911,7 +3911,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0.42;0.44;0.6</t>
+          <t>0.6;0.42;0.44</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -3969,12 +3969,12 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>rs1065852,rs1058164,rs1135840</t>
+          <t>rs1135840,rs1065852,rs1058164</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>chr22:42129130:C&gt;G,chr22:42126611:C&gt;G,chr22:42130692:G&gt;A</t>
+          <t>chr22:42129130:C&gt;G,chr22:42130692:G&gt;A,chr22:42126611:C&gt;G</t>
         </is>
       </c>
     </row>
@@ -3991,7 +3991,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>314.64,577.64,513.64</t>
+          <t>314.64,513.64,577.64</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -4001,7 +4001,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0.42;0.44;0.6</t>
+          <t>0.6;0.42;0.44</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -4053,12 +4053,12 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>rs1065852,rs1058164,rs1135840</t>
+          <t>rs1135840,rs1065852,rs1058164</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>chr22:42129130:C&gt;G,chr22:42126611:C&gt;G,chr22:42130692:G&gt;A</t>
+          <t>chr22:42129130:C&gt;G,chr22:42130692:G&gt;A,chr22:42126611:C&gt;G</t>
         </is>
       </c>
     </row>
@@ -4075,7 +4075,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>314.64,577.64,513.64</t>
+          <t>314.64,513.64,577.64</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -4085,7 +4085,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0.42;0.44;0.6</t>
+          <t>0.6;0.42;0.44</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>rs1065852,rs1058164,rs1135840</t>
+          <t>rs1135840,rs1065852,rs1058164</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>chr22:42129130:C&gt;G,chr22:42126611:C&gt;G,chr22:42130692:G&gt;A</t>
+          <t>chr22:42129130:C&gt;G,chr22:42130692:G&gt;A,chr22:42126611:C&gt;G</t>
         </is>
       </c>
     </row>
@@ -4163,7 +4163,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>314.64,577.64,513.64</t>
+          <t>314.64,513.64,577.64</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -4173,7 +4173,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0.42;0.44;0.6</t>
+          <t>0.6;0.42;0.44</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -4231,12 +4231,12 @@
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>rs1065852,rs1058164,rs1135840</t>
+          <t>rs1135840,rs1065852,rs1058164</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>chr22:42129130:C&gt;G,chr22:42126611:C&gt;G,chr22:42130692:G&gt;A</t>
+          <t>chr22:42129130:C&gt;G,chr22:42130692:G&gt;A,chr22:42126611:C&gt;G</t>
         </is>
       </c>
     </row>
@@ -4253,7 +4253,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>314.64,577.64,513.64</t>
+          <t>314.64,513.64,577.64</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -4263,7 +4263,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0.42;0.44;0.6</t>
+          <t>0.6;0.42;0.44</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>rs1065852,rs1058164,rs1135840</t>
+          <t>rs1135840,rs1065852,rs1058164</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>chr22:42129130:C&gt;G,chr22:42126611:C&gt;G,chr22:42130692:G&gt;A</t>
+          <t>chr22:42129130:C&gt;G,chr22:42130692:G&gt;A,chr22:42126611:C&gt;G</t>
         </is>
       </c>
     </row>
@@ -4341,7 +4341,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>314.64,577.64,513.64</t>
+          <t>314.64,513.64,577.64</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0.42;0.44;0.6</t>
+          <t>0.6;0.42;0.44</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>rs1065852,rs1058164,rs1135840</t>
+          <t>rs1135840,rs1065852,rs1058164</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>chr22:42129130:C&gt;G,chr22:42126611:C&gt;G,chr22:42130692:G&gt;A</t>
+          <t>chr22:42129130:C&gt;G,chr22:42130692:G&gt;A,chr22:42126611:C&gt;G</t>
         </is>
       </c>
     </row>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>314.64,577.64,513.64</t>
+          <t>314.64,513.64,577.64</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0.42;0.44;0.6</t>
+          <t>0.6;0.42;0.44</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -4497,12 +4497,12 @@
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>rs1065852,rs1058164,rs1135840</t>
+          <t>rs1135840,rs1065852,rs1058164</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>chr22:42129130:C&gt;G,chr22:42126611:C&gt;G,chr22:42130692:G&gt;A</t>
+          <t>chr22:42129130:C&gt;G,chr22:42130692:G&gt;A,chr22:42126611:C&gt;G</t>
         </is>
       </c>
     </row>
@@ -4519,7 +4519,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>314.64,577.64,513.64</t>
+          <t>314.64,513.64,577.64</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -4529,7 +4529,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0.42;0.44;0.6</t>
+          <t>0.6;0.42;0.44</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -4587,12 +4587,12 @@
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>rs1065852,rs1058164,rs1135840</t>
+          <t>rs1135840,rs1065852,rs1058164</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>chr22:42129130:C&gt;G,chr22:42126611:C&gt;G,chr22:42130692:G&gt;A</t>
+          <t>chr22:42129130:C&gt;G,chr22:42130692:G&gt;A,chr22:42126611:C&gt;G</t>
         </is>
       </c>
     </row>
@@ -4609,7 +4609,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>314.64,577.64,513.64</t>
+          <t>314.64,513.64,577.64</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -4619,7 +4619,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0.42;0.44;0.6</t>
+          <t>0.6;0.42;0.44</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>rs1065852,rs1058164,rs1135840</t>
+          <t>rs1135840,rs1065852,rs1058164</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>chr22:42129130:C&gt;G,chr22:42126611:C&gt;G,chr22:42130692:G&gt;A</t>
+          <t>chr22:42129130:C&gt;G,chr22:42130692:G&gt;A,chr22:42126611:C&gt;G</t>
         </is>
       </c>
     </row>
@@ -4699,7 +4699,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>314.64,577.64,513.64</t>
+          <t>314.64,513.64,577.64</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -4709,7 +4709,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0.42;0.44;0.6</t>
+          <t>0.6;0.42;0.44</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -4795,12 +4795,12 @@
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>rs1065852,rs1058164,rs1135840</t>
+          <t>rs1135840,rs1065852,rs1058164</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>chr22:42129130:C&gt;G,chr22:42126611:C&gt;G,chr22:42130692:G&gt;A</t>
+          <t>chr22:42129130:C&gt;G,chr22:42130692:G&gt;A,chr22:42126611:C&gt;G</t>
         </is>
       </c>
     </row>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>314.64,577.64,513.64</t>
+          <t>314.64,513.64,577.64</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -4827,7 +4827,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0.42;0.44;0.6</t>
+          <t>0.6;0.42;0.44</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -4883,12 +4883,12 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>rs1065852,rs1058164,rs1135840</t>
+          <t>rs1135840,rs1065852,rs1058164</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>chr22:42129130:C&gt;G,chr22:42126611:C&gt;G,chr22:42130692:G&gt;A</t>
+          <t>chr22:42129130:C&gt;G,chr22:42130692:G&gt;A,chr22:42126611:C&gt;G</t>
         </is>
       </c>
     </row>
@@ -4905,7 +4905,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>314.64,577.64,513.64</t>
+          <t>314.64,513.64,577.64</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -4915,7 +4915,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0.42;0.44;0.6</t>
+          <t>0.6;0.42;0.44</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>rs1065852,rs1058164,rs1135840</t>
+          <t>rs1135840,rs1065852,rs1058164</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>chr22:42129130:C&gt;G,chr22:42126611:C&gt;G,chr22:42130692:G&gt;A</t>
+          <t>chr22:42129130:C&gt;G,chr22:42130692:G&gt;A,chr22:42126611:C&gt;G</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>314.64,577.64,513.64</t>
+          <t>314.64,513.64,577.64</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0.42;0.44;0.6</t>
+          <t>0.6;0.42;0.44</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -5061,12 +5061,12 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>rs1065852,rs1058164,rs1135840</t>
+          <t>rs1135840,rs1065852,rs1058164</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>chr22:42129130:C&gt;G,chr22:42126611:C&gt;G,chr22:42130692:G&gt;A</t>
+          <t>chr22:42129130:C&gt;G,chr22:42130692:G&gt;A,chr22:42126611:C&gt;G</t>
         </is>
       </c>
     </row>
@@ -5083,7 +5083,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>314.64,577.64,513.64</t>
+          <t>314.64,513.64,577.64</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -5093,7 +5093,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0.42;0.44;0.6</t>
+          <t>0.6;0.42;0.44</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -5149,12 +5149,12 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>rs1065852,rs1058164,rs1135840</t>
+          <t>rs1135840,rs1065852,rs1058164</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>chr22:42129130:C&gt;G,chr22:42126611:C&gt;G,chr22:42130692:G&gt;A</t>
+          <t>chr22:42129130:C&gt;G,chr22:42130692:G&gt;A,chr22:42126611:C&gt;G</t>
         </is>
       </c>
     </row>
@@ -5171,7 +5171,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>314.64,577.64,513.64</t>
+          <t>314.64,513.64,577.64</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -5181,7 +5181,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0.42;0.44;0.6</t>
+          <t>0.6;0.42;0.44</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -5237,12 +5237,12 @@
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>rs1065852,rs1058164,rs1135840</t>
+          <t>rs1135840,rs1065852,rs1058164</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>chr22:42129130:C&gt;G,chr22:42126611:C&gt;G,chr22:42130692:G&gt;A</t>
+          <t>chr22:42129130:C&gt;G,chr22:42130692:G&gt;A,chr22:42126611:C&gt;G</t>
         </is>
       </c>
     </row>
@@ -5259,7 +5259,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>314.64,577.64,513.64</t>
+          <t>314.64,513.64,577.64</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -5269,7 +5269,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0.42;0.44;0.6</t>
+          <t>0.6;0.42;0.44</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -5327,12 +5327,12 @@
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>rs1065852,rs1058164,rs1135840</t>
+          <t>rs1135840,rs1065852,rs1058164</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>chr22:42129130:C&gt;G,chr22:42126611:C&gt;G,chr22:42130692:G&gt;A</t>
+          <t>chr22:42129130:C&gt;G,chr22:42130692:G&gt;A,chr22:42126611:C&gt;G</t>
         </is>
       </c>
     </row>
@@ -5349,7 +5349,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>314.64,577.64,513.64</t>
+          <t>314.64,513.64,577.64</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -5359,7 +5359,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0.42;0.44;0.6</t>
+          <t>0.6;0.42;0.44</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -5417,12 +5417,12 @@
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>rs1065852,rs1058164,rs1135840</t>
+          <t>rs1135840,rs1065852,rs1058164</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>chr22:42129130:C&gt;G,chr22:42126611:C&gt;G,chr22:42130692:G&gt;A</t>
+          <t>chr22:42129130:C&gt;G,chr22:42130692:G&gt;A,chr22:42126611:C&gt;G</t>
         </is>
       </c>
     </row>
@@ -5439,7 +5439,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>314.64,577.64,513.64</t>
+          <t>314.64,513.64,577.64</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -5449,7 +5449,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0.42;0.44;0.6</t>
+          <t>0.6;0.42;0.44</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -5508,12 +5508,12 @@
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>rs1065852,rs1058164,rs1135840</t>
+          <t>rs1135840,rs1065852,rs1058164</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>chr22:42129130:C&gt;G,chr22:42126611:C&gt;G,chr22:42130692:G&gt;A</t>
+          <t>chr22:42129130:C&gt;G,chr22:42130692:G&gt;A,chr22:42126611:C&gt;G</t>
         </is>
       </c>
     </row>
@@ -5530,7 +5530,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>314.64,577.64,513.64</t>
+          <t>314.64,513.64,577.64</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -5540,7 +5540,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0.42;0.44;0.6</t>
+          <t>0.6;0.42;0.44</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -5600,12 +5600,12 @@
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>rs1065852,rs1058164,rs1135840</t>
+          <t>rs1135840,rs1065852,rs1058164</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>chr22:42129130:C&gt;G,chr22:42126611:C&gt;G,chr22:42130692:G&gt;A</t>
+          <t>chr22:42129130:C&gt;G,chr22:42130692:G&gt;A,chr22:42126611:C&gt;G</t>
         </is>
       </c>
     </row>
@@ -5622,7 +5622,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>314.64,577.64,513.64</t>
+          <t>314.64,513.64,577.64</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -5632,7 +5632,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0.42;0.44;0.6</t>
+          <t>0.6;0.42;0.44</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -5692,12 +5692,12 @@
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>rs1065852,rs1058164,rs1135840</t>
+          <t>rs1135840,rs1065852,rs1058164</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>chr22:42129130:C&gt;G,chr22:42126611:C&gt;G,chr22:42130692:G&gt;A</t>
+          <t>chr22:42129130:C&gt;G,chr22:42130692:G&gt;A,chr22:42126611:C&gt;G</t>
         </is>
       </c>
     </row>
@@ -5714,7 +5714,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>314.64,577.64,513.64</t>
+          <t>314.64,513.64,577.64</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -5724,7 +5724,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0.42;0.44;0.6</t>
+          <t>0.6;0.42;0.44</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -5780,12 +5780,12 @@
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>rs1065852,rs1058164,rs1135840</t>
+          <t>rs1135840,rs1065852,rs1058164</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>chr22:42129130:C&gt;G,chr22:42126611:C&gt;G,chr22:42130692:G&gt;A</t>
+          <t>chr22:42129130:C&gt;G,chr22:42130692:G&gt;A,chr22:42126611:C&gt;G</t>
         </is>
       </c>
     </row>
@@ -5802,7 +5802,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>314.64,577.64,513.64</t>
+          <t>314.64,513.64,577.64</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -5812,7 +5812,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0.42;0.44;0.6</t>
+          <t>0.6;0.42;0.44</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -5868,12 +5868,12 @@
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>rs1065852,rs1058164,rs1135840</t>
+          <t>rs1135840,rs1065852,rs1058164</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>chr22:42129130:C&gt;G,chr22:42126611:C&gt;G,chr22:42130692:G&gt;A</t>
+          <t>chr22:42129130:C&gt;G,chr22:42130692:G&gt;A,chr22:42126611:C&gt;G</t>
         </is>
       </c>
     </row>
@@ -5890,7 +5890,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>314.64,577.64,513.64</t>
+          <t>314.64,513.64,577.64</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -5900,7 +5900,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0.42;0.44;0.6</t>
+          <t>0.6;0.42;0.44</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -5960,12 +5960,12 @@
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>rs1065852,rs1058164,rs1135840</t>
+          <t>rs1135840,rs1065852,rs1058164</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>chr22:42129130:C&gt;G,chr22:42126611:C&gt;G,chr22:42130692:G&gt;A</t>
+          <t>chr22:42129130:C&gt;G,chr22:42130692:G&gt;A,chr22:42126611:C&gt;G</t>
         </is>
       </c>
     </row>
@@ -5982,7 +5982,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>314.64,577.64,513.64</t>
+          <t>314.64,513.64,577.64</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -5992,7 +5992,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0.42;0.44;0.6</t>
+          <t>0.6;0.42;0.44</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -6044,12 +6044,12 @@
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>rs1065852,rs1058164,rs1135840</t>
+          <t>rs1135840,rs1065852,rs1058164</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>chr22:42129130:C&gt;G,chr22:42126611:C&gt;G,chr22:42130692:G&gt;A</t>
+          <t>chr22:42129130:C&gt;G,chr22:42130692:G&gt;A,chr22:42126611:C&gt;G</t>
         </is>
       </c>
     </row>
@@ -6066,7 +6066,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>314.64,577.64,513.64</t>
+          <t>314.64,513.64,577.64</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -6076,7 +6076,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0.42;0.44;0.6</t>
+          <t>0.6;0.42;0.44</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -6132,12 +6132,12 @@
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>rs1065852,rs1058164,rs1135840</t>
+          <t>rs1135840,rs1065852,rs1058164</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>chr22:42129130:C&gt;G,chr22:42126611:C&gt;G,chr22:42130692:G&gt;A</t>
+          <t>chr22:42129130:C&gt;G,chr22:42130692:G&gt;A,chr22:42126611:C&gt;G</t>
         </is>
       </c>
     </row>
@@ -6154,7 +6154,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>314.64,577.64,513.64</t>
+          <t>314.64,513.64,577.64</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -6164,7 +6164,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0.42;0.44;0.6</t>
+          <t>0.6;0.42;0.44</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -6222,12 +6222,12 @@
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>rs1065852,rs1058164,rs1135840</t>
+          <t>rs1135840,rs1065852,rs1058164</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>chr22:42129130:C&gt;G,chr22:42126611:C&gt;G,chr22:42130692:G&gt;A</t>
+          <t>chr22:42129130:C&gt;G,chr22:42130692:G&gt;A,chr22:42126611:C&gt;G</t>
         </is>
       </c>
     </row>
@@ -6244,7 +6244,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>314.64,577.64,513.64</t>
+          <t>314.64,513.64,577.64</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -6254,7 +6254,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>0.42;0.44;0.6</t>
+          <t>0.6;0.42;0.44</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>rs1065852,rs1058164,rs1135840</t>
+          <t>rs1135840,rs1065852,rs1058164</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>chr22:42129130:C&gt;G,chr22:42126611:C&gt;G,chr22:42130692:G&gt;A</t>
+          <t>chr22:42129130:C&gt;G,chr22:42130692:G&gt;A,chr22:42126611:C&gt;G</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>314.64,577.64,513.64</t>
+          <t>314.64,513.64,577.64</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0.42;0.44;0.6</t>
+          <t>0.6;0.42;0.44</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -6400,12 +6400,12 @@
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>rs1065852,rs1058164,rs1135840</t>
+          <t>rs1135840,rs1065852,rs1058164</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>chr22:42129130:C&gt;G,chr22:42126611:C&gt;G,chr22:42130692:G&gt;A</t>
+          <t>chr22:42129130:C&gt;G,chr22:42130692:G&gt;A,chr22:42126611:C&gt;G</t>
         </is>
       </c>
     </row>
@@ -6422,7 +6422,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>314.64,577.64,513.64</t>
+          <t>314.64,513.64,577.64</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -6432,7 +6432,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0.42;0.44;0.6</t>
+          <t>0.6;0.42;0.44</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -6488,12 +6488,12 @@
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>rs1065852,rs1058164,rs1135840</t>
+          <t>rs1135840,rs1065852,rs1058164</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>chr22:42129130:C&gt;G,chr22:42126611:C&gt;G,chr22:42130692:G&gt;A</t>
+          <t>chr22:42129130:C&gt;G,chr22:42130692:G&gt;A,chr22:42126611:C&gt;G</t>
         </is>
       </c>
     </row>
@@ -9160,12 +9160,12 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>1536.06,1829.06</t>
+          <t>1829.06,1536.06</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>0,55;0,47</t>
+          <t>0,47;0,55</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -9228,12 +9228,12 @@
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>rs2306283,rs4149056</t>
+          <t>rs4149056,rs2306283</t>
         </is>
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>chr12:21176804:A&gt;G,chr12:21178615:T&gt;C</t>
+          <t>chr12:21178615:T&gt;C,chr12:21176804:A&gt;G</t>
         </is>
       </c>
     </row>
@@ -9250,12 +9250,12 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>1536.06,1829.06</t>
+          <t>1829.06,1536.06</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>0,55;0,47</t>
+          <t>0,47;0,55</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -9312,12 +9312,12 @@
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>rs2306283,rs4149056</t>
+          <t>rs4149056,rs2306283</t>
         </is>
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>chr12:21176804:A&gt;G,chr12:21178615:T&gt;C</t>
+          <t>chr12:21178615:T&gt;C,chr12:21176804:A&gt;G</t>
         </is>
       </c>
     </row>
@@ -9334,12 +9334,12 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>1536.06,1829.06</t>
+          <t>1829.06,1536.06</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>0,55;0,47</t>
+          <t>0,47;0,55</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -9402,12 +9402,12 @@
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>rs2306283,rs4149056</t>
+          <t>rs4149056,rs2306283</t>
         </is>
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>chr12:21176804:A&gt;G,chr12:21178615:T&gt;C</t>
+          <t>chr12:21178615:T&gt;C,chr12:21176804:A&gt;G</t>
         </is>
       </c>
     </row>
@@ -9424,12 +9424,12 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>1536.06,1829.06</t>
+          <t>1829.06,1536.06</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>0,55;0,47</t>
+          <t>0,47;0,55</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>rs2306283,rs4149056</t>
+          <t>rs4149056,rs2306283</t>
         </is>
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>chr12:21176804:A&gt;G,chr12:21178615:T&gt;C</t>
+          <t>chr12:21178615:T&gt;C,chr12:21176804:A&gt;G</t>
         </is>
       </c>
     </row>
@@ -9514,12 +9514,12 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>1536.06,1829.06</t>
+          <t>1829.06,1536.06</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>0,55;0,47</t>
+          <t>0,47;0,55</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -9582,12 +9582,12 @@
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>rs2306283,rs4149056</t>
+          <t>rs4149056,rs2306283</t>
         </is>
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>chr12:21176804:A&gt;G,chr12:21178615:T&gt;C</t>
+          <t>chr12:21178615:T&gt;C,chr12:21176804:A&gt;G</t>
         </is>
       </c>
     </row>
@@ -9604,12 +9604,12 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>1536.06,1829.06</t>
+          <t>1829.06,1536.06</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>0,55;0,47</t>
+          <t>0,47;0,55</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>rs2306283,rs4149056</t>
+          <t>rs4149056,rs2306283</t>
         </is>
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>chr12:21176804:A&gt;G,chr12:21178615:T&gt;C</t>
+          <t>chr12:21178615:T&gt;C,chr12:21176804:A&gt;G</t>
         </is>
       </c>
     </row>
@@ -9694,12 +9694,12 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>1536.06,1829.06</t>
+          <t>1829.06,1536.06</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>0,55;0,47</t>
+          <t>0,47;0,55</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -9762,12 +9762,12 @@
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>rs2306283,rs4149056</t>
+          <t>rs4149056,rs2306283</t>
         </is>
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>chr12:21176804:A&gt;G,chr12:21178615:T&gt;C</t>
+          <t>chr12:21178615:T&gt;C,chr12:21176804:A&gt;G</t>
         </is>
       </c>
     </row>
@@ -9784,12 +9784,12 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>1536.06,1829.06</t>
+          <t>1829.06,1536.06</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>0,55;0,47</t>
+          <t>0,47;0,55</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -9852,12 +9852,12 @@
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>rs2306283,rs4149056</t>
+          <t>rs4149056,rs2306283</t>
         </is>
       </c>
       <c r="R106" t="inlineStr">
         <is>
-          <t>chr12:21176804:A&gt;G,chr12:21178615:T&gt;C</t>
+          <t>chr12:21178615:T&gt;C,chr12:21176804:A&gt;G</t>
         </is>
       </c>
     </row>
